--- a/result/Table202507.xlsx
+++ b/result/Table202507.xlsx
@@ -516,24 +516,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
         <v>6.43</v>
       </c>
       <c r="J2" t="n">
-        <v>8.029999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="K2" t="n">
-        <v>24.88</v>
+        <v>18.35</v>
       </c>
       <c r="L2" t="n">
-        <v>24883.36</v>
+        <v>18351.48</v>
       </c>
     </row>
     <row r="3">
@@ -612,24 +612,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.69</v>
+        <v>4.28</v>
       </c>
       <c r="K4" t="n">
-        <v>11.67</v>
+        <v>1.9</v>
       </c>
       <c r="L4" t="n">
-        <v>11666.67</v>
+        <v>1904.76</v>
       </c>
     </row>
     <row r="5">
@@ -658,24 +658,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>30.6</v>
       </c>
       <c r="J5" t="n">
-        <v>28.55</v>
+        <v>27.1</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.7</v>
+        <v>-11.44</v>
       </c>
       <c r="L5" t="n">
-        <v>-6699.35</v>
+        <v>-11437.91</v>
       </c>
     </row>
     <row r="6">
@@ -704,24 +704,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
         <v>4.35</v>
       </c>
       <c r="J6" t="n">
-        <v>4.29</v>
+        <v>4.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.38</v>
+        <v>-6.44</v>
       </c>
       <c r="L6" t="n">
-        <v>-1379.31</v>
+        <v>-6436.78</v>
       </c>
     </row>
     <row r="7">
@@ -800,24 +800,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
         <v>33.43</v>
       </c>
       <c r="J8" t="n">
-        <v>34.11</v>
+        <v>45.46</v>
       </c>
       <c r="K8" t="n">
-        <v>2.03</v>
+        <v>35.99</v>
       </c>
       <c r="L8" t="n">
-        <v>2034.1</v>
+        <v>35985.64</v>
       </c>
     </row>
     <row r="9">
@@ -946,24 +946,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>44.81</v>
       </c>
       <c r="J11" t="n">
-        <v>54.07</v>
+        <v>52.86</v>
       </c>
       <c r="K11" t="n">
-        <v>20.67</v>
+        <v>17.96</v>
       </c>
       <c r="L11" t="n">
-        <v>20665.03</v>
+        <v>17964.74</v>
       </c>
     </row>
     <row r="12">
@@ -992,24 +992,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>52.61</v>
       </c>
       <c r="J12" t="n">
-        <v>49.6</v>
+        <v>46.87</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.72</v>
+        <v>-10.91</v>
       </c>
       <c r="L12" t="n">
-        <v>-5721.35</v>
+        <v>-10910.47</v>
       </c>
     </row>
     <row r="13">
@@ -1084,24 +1084,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
         <v>14.99</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4</v>
+        <v>14.83</v>
       </c>
       <c r="K14" t="n">
-        <v>2.74</v>
+        <v>-1.07</v>
       </c>
       <c r="L14" t="n">
-        <v>2735.16</v>
+        <v>-1067.38</v>
       </c>
     </row>
     <row r="15">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
         <v>17.8</v>
       </c>
       <c r="J16" t="n">
-        <v>17.94</v>
+        <v>17.1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.79</v>
+        <v>-3.93</v>
       </c>
       <c r="L16" t="n">
-        <v>786.52</v>
+        <v>-3932.58</v>
       </c>
     </row>
     <row r="17">
@@ -1422,24 +1422,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>4.09</v>
       </c>
       <c r="J21" t="n">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.07</v>
+        <v>-14.91</v>
       </c>
       <c r="L21" t="n">
-        <v>-8068.46</v>
+        <v>-14914.43</v>
       </c>
     </row>
     <row r="22">
@@ -1518,24 +1518,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
         <v>12.87</v>
       </c>
       <c r="J23" t="n">
-        <v>11.99</v>
+        <v>11.51</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.84</v>
+        <v>-10.57</v>
       </c>
       <c r="L23" t="n">
-        <v>-6837.61</v>
+        <v>-10567.21</v>
       </c>
     </row>
     <row r="24">
@@ -1664,24 +1664,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
         <v>5.5</v>
       </c>
       <c r="J26" t="n">
-        <v>6.32</v>
+        <v>6.18</v>
       </c>
       <c r="K26" t="n">
-        <v>14.91</v>
+        <v>12.36</v>
       </c>
       <c r="L26" t="n">
-        <v>14909.09</v>
+        <v>12363.64</v>
       </c>
     </row>
     <row r="27">
@@ -1910,24 +1910,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I31" t="n">
         <v>89.5</v>
       </c>
       <c r="J31" t="n">
-        <v>83.01000000000001</v>
+        <v>142.93</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.25</v>
+        <v>59.7</v>
       </c>
       <c r="L31" t="n">
-        <v>-7251.4</v>
+        <v>59698.32</v>
       </c>
     </row>
     <row r="32">
@@ -2006,24 +2006,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I33" t="n">
         <v>24.1</v>
       </c>
       <c r="J33" t="n">
-        <v>22.62</v>
+        <v>21.61</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.14</v>
+        <v>-10.33</v>
       </c>
       <c r="L33" t="n">
-        <v>-6141.08</v>
+        <v>-10331.95</v>
       </c>
     </row>
     <row r="34">
@@ -2052,24 +2052,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>38.25</v>
       </c>
       <c r="J34" t="n">
-        <v>34.79</v>
+        <v>33.49</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.050000000000001</v>
+        <v>-12.44</v>
       </c>
       <c r="L34" t="n">
-        <v>-9045.75</v>
+        <v>-12444.44</v>
       </c>
     </row>
     <row r="35">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
         <v>20.13</v>
       </c>
       <c r="J35" t="n">
-        <v>18.37</v>
+        <v>20.93</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.74</v>
+        <v>3.97</v>
       </c>
       <c r="L35" t="n">
-        <v>-8743.17</v>
+        <v>3974.17</v>
       </c>
     </row>
     <row r="36">
@@ -2244,24 +2244,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
         <v>7.1</v>
       </c>
       <c r="J38" t="n">
-        <v>6.61</v>
+        <v>6.3</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.9</v>
+        <v>-11.27</v>
       </c>
       <c r="L38" t="n">
-        <v>-6901.41</v>
+        <v>-11267.61</v>
       </c>
     </row>
     <row r="39">
@@ -2436,24 +2436,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
         <v>18.16</v>
       </c>
       <c r="J42" t="n">
-        <v>17.28</v>
+        <v>16.59</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.85</v>
+        <v>-8.65</v>
       </c>
       <c r="L42" t="n">
-        <v>-4845.81</v>
+        <v>-8645.370000000001</v>
       </c>
     </row>
     <row r="43">
@@ -2532,24 +2532,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I44" t="n">
         <v>10.2</v>
       </c>
       <c r="J44" t="n">
-        <v>11.01</v>
+        <v>10.43</v>
       </c>
       <c r="K44" t="n">
-        <v>7.94</v>
+        <v>2.25</v>
       </c>
       <c r="L44" t="n">
-        <v>7941.18</v>
+        <v>2254.9</v>
       </c>
     </row>
     <row r="45">
